--- a/dist/output/detailed.xlsx
+++ b/dist/output/detailed.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP5"/>
+  <dimension ref="A1:FY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1151,10 +1151,185 @@
       </c>
       <c r="EO1" s="1" t="inlineStr">
         <is>
+          <t>Q141</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
+        <is>
+          <t>Q142</t>
+        </is>
+      </c>
+      <c r="EQ1" s="1" t="inlineStr">
+        <is>
+          <t>Q143</t>
+        </is>
+      </c>
+      <c r="ER1" s="1" t="inlineStr">
+        <is>
+          <t>Q144</t>
+        </is>
+      </c>
+      <c r="ES1" s="1" t="inlineStr">
+        <is>
+          <t>Q145</t>
+        </is>
+      </c>
+      <c r="ET1" s="1" t="inlineStr">
+        <is>
+          <t>Q146</t>
+        </is>
+      </c>
+      <c r="EU1" s="1" t="inlineStr">
+        <is>
+          <t>Q147</t>
+        </is>
+      </c>
+      <c r="EV1" s="1" t="inlineStr">
+        <is>
+          <t>Q148</t>
+        </is>
+      </c>
+      <c r="EW1" s="1" t="inlineStr">
+        <is>
+          <t>Q149</t>
+        </is>
+      </c>
+      <c r="EX1" s="1" t="inlineStr">
+        <is>
+          <t>Q150</t>
+        </is>
+      </c>
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>Q151</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>Q152</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>Q153</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>Q154</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>Q155</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>Q156</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>Q157</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>Q158</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>Q159</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>Q160</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>Q161</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>Q162</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>Q163</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>Q164</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>Q165</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>Q166</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>Q167</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>Q168</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
+        <is>
+          <t>Q169</t>
+        </is>
+      </c>
+      <c r="FR1" s="1" t="inlineStr">
+        <is>
+          <t>Q170</t>
+        </is>
+      </c>
+      <c r="FS1" s="1" t="inlineStr">
+        <is>
+          <t>Q171</t>
+        </is>
+      </c>
+      <c r="FT1" s="1" t="inlineStr">
+        <is>
+          <t>Q172</t>
+        </is>
+      </c>
+      <c r="FU1" s="1" t="inlineStr">
+        <is>
+          <t>Q173</t>
+        </is>
+      </c>
+      <c r="FV1" s="1" t="inlineStr">
+        <is>
+          <t>Q174</t>
+        </is>
+      </c>
+      <c r="FW1" s="1" t="inlineStr">
+        <is>
+          <t>Q175</t>
+        </is>
+      </c>
+      <c r="FX1" s="1" t="inlineStr">
+        <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="FY1" s="1" t="inlineStr">
         <is>
           <t>Grade</t>
         </is>
@@ -1166,12 +1341,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>UP24JDA222615</t>
+          <t>UP28SWF234567</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0125</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1191,402 +1366,402 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1596,7 +1771,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
@@ -1606,7 +1781,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1616,42 +1791,42 @@
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CV2" t="inlineStr">
@@ -1661,17 +1836,17 @@
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CY2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CZ2" t="inlineStr">
@@ -1686,7 +1861,7 @@
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DC2" t="inlineStr">
@@ -1696,27 +1871,27 @@
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="DG2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
@@ -1726,22 +1901,22 @@
       </c>
       <c r="DJ2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="DK2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
@@ -1751,47 +1926,47 @@
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="DR2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DT2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DU2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
@@ -1801,12 +1976,12 @@
       </c>
       <c r="DY2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DZ2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="EA2" t="inlineStr">
@@ -1816,52 +1991,52 @@
       </c>
       <c r="EB2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="EC2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="ED2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="EE2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="EF2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="EG2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="EH2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="EI2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="EJ2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="EK2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr">
@@ -1871,18 +2046,193 @@
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="EO2" t="n">
-        <v>75</v>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="EP2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EW2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EZ2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FA2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FB2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FC2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FD2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FE2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FF2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FG2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FH2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FI2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FJ2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FK2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FL2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FM2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FN2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FO2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FP2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FQ2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FR2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FS2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FT2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FU2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FV2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FW2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FX2" t="n">
+        <v>68</v>
+      </c>
+      <c r="FY2" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -1894,42 +2244,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UP24JDA250429</t>
+          <t>UP27SDF123456</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1949,12 +2299,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1979,52 +2329,52 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -2044,17 +2394,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -2069,27 +2419,27 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
@@ -2104,62 +2454,62 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
@@ -2169,17 +2519,17 @@
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -2199,12 +2549,12 @@
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -2224,22 +2574,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -2249,27 +2599,27 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -2279,12 +2629,12 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>M</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -2299,22 +2649,22 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -2329,7 +2679,7 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
@@ -2349,268 +2699,443 @@
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CU3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DA3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DB3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DD3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DE3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DF3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DG3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DI3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DJ3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DK3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DL3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DN3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DO3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DP3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DQ3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DS3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DT3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DU3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DV3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DW3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DX3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DY3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DZ3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EA3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EB3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EC3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="ED3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EE3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EF3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EG3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EH3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EI3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EJ3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EK3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EL3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EM3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EN3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EO3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EP3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EQ3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="ER3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="ES3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="ET3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EU3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EV3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EW3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EX3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EY3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EZ3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FA3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FB3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="FC3" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="CU3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="CV3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="CW3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="CX3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="CY3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="CZ3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="DA3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="DB3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="DC3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="DD3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="DE3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="DF3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="DG3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="DH3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="DI3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="DJ3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="DK3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="DL3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="DM3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="DN3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="DO3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="DP3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="DQ3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="DR3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="DS3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="DT3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="DU3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="DV3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="DW3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="DX3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="DY3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="DZ3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="EA3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="EB3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="EC3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="ED3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="EE3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="EF3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="EG3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="EH3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="EI3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="EJ3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="EK3" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="EL3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="EM3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="EN3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="EO3" t="n">
-        <v>85</v>
-      </c>
-      <c r="EP3" t="inlineStr">
+      <c r="FD3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FE3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FF3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FG3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FH3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FI3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FJ3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FK3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FL3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FM3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FN3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FO3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FP3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FQ3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FR3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FS3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FT3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FU3" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FV3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FW3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FX3" t="n">
+        <v>72</v>
+      </c>
+      <c r="FY3" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -2622,17 +3147,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>UP24JDA250614</t>
+          <t>UP24SWF456789</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0141</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2642,32 +3167,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2677,37 +3202,37 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -2727,12 +3252,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -2742,97 +3267,97 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2842,52 +3367,52 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
@@ -2902,7 +3427,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
@@ -2912,17 +3437,17 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
@@ -2932,42 +3457,42 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>-</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2977,7 +3502,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -3002,17 +3527,17 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -3027,27 +3552,27 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -3062,17 +3587,17 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
@@ -3087,77 +3612,77 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="CX4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CY4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="DC4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DD4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DE4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="DF4" t="inlineStr">
@@ -3167,27 +3692,27 @@
       </c>
       <c r="DG4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DH4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="DI4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DJ4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="DK4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DL4" t="inlineStr">
@@ -3197,17 +3722,17 @@
       </c>
       <c r="DM4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>M</t>
         </is>
       </c>
       <c r="DN4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DO4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DP4" t="inlineStr">
@@ -3217,7 +3742,7 @@
       </c>
       <c r="DQ4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="DR4" t="inlineStr">
@@ -3227,12 +3752,12 @@
       </c>
       <c r="DS4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DT4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DU4" t="inlineStr">
@@ -3247,27 +3772,27 @@
       </c>
       <c r="DW4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DX4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DY4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DZ4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="EA4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="EB4" t="inlineStr">
@@ -3277,22 +3802,22 @@
       </c>
       <c r="EC4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="ED4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="EE4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="EF4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="EG4" t="inlineStr">
@@ -3307,12 +3832,12 @@
       </c>
       <c r="EI4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="EJ4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="EK4" t="inlineStr">
@@ -3327,18 +3852,193 @@
       </c>
       <c r="EM4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="EN4" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="EO4" t="n">
-        <v>87.5</v>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EO4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
       </c>
       <c r="EP4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EQ4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="ER4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="ES4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="ET4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EU4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EV4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EW4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EX4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EY4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EZ4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FA4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FB4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FC4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FD4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FE4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FF4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FG4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FH4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FI4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FJ4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FK4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FL4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FM4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FN4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FO4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FP4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FQ4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FR4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FS4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FT4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FU4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FV4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FW4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FX4" t="n">
+        <v>76</v>
+      </c>
+      <c r="FY4" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -3350,12 +4050,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UP24JDA250617</t>
+          <t>UP20SDA890123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0123</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3375,22 +4075,22 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -3415,42 +4115,42 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -3460,32 +4160,32 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
@@ -3500,17 +4200,17 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -3530,7 +4230,7 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -3540,32 +4240,32 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
@@ -3575,42 +4275,42 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -3635,37 +4335,37 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -3680,12 +4380,12 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -3695,7 +4395,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -3715,37 +4415,37 @@
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -3755,7 +4455,7 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
@@ -3770,67 +4470,67 @@
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -3840,12 +4540,12 @@
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="CX5" t="inlineStr">
@@ -3890,22 +4590,22 @@
       </c>
       <c r="DF5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DG5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="DH5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="DI5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DJ5" t="inlineStr">
@@ -3915,12 +4615,12 @@
       </c>
       <c r="DK5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="DL5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DM5" t="inlineStr">
@@ -3930,27 +4630,27 @@
       </c>
       <c r="DN5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DO5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="DP5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DQ5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="DR5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DS5" t="inlineStr">
@@ -3965,12 +4665,12 @@
       </c>
       <c r="DU5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="DV5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DW5" t="inlineStr">
@@ -3980,12 +4680,12 @@
       </c>
       <c r="DX5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="DY5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="DZ5" t="inlineStr">
@@ -3995,62 +4695,62 @@
       </c>
       <c r="EA5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="EB5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="EC5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="ED5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="EE5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="EF5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="EG5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="EH5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="EI5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="EJ5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="EK5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="EL5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="EM5" t="inlineStr">
@@ -4060,13 +4760,4703 @@
       </c>
       <c r="EN5" t="inlineStr">
         <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="EO5" t="n">
-        <v>95</v>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EO5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
       </c>
       <c r="EP5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EQ5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="ER5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="ES5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="ET5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EU5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EV5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EW5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EX5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EY5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EZ5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FA5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FB5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FC5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FD5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FE5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FF5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FG5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FH5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FI5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FJ5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FK5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FL5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FM5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FN5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FO5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FP5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FQ5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FR5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FS5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FT5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FU5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FV5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FW5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FX5" t="n">
+        <v>90</v>
+      </c>
+      <c r="FY5" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>UP21SDF789012</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DA6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DB6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DD6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DF6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DG6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DI6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DJ6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DK6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DL6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DN6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DO6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DP6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DQ6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DS6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DT6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DU6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DV6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DW6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DX6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DY6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DZ6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EA6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EB6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EC6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="ED6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EE6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EF6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EG6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EH6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EI6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EJ6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EK6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EL6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EM6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EN6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EO6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EP6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EQ6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="ER6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="ES6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="ET6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EU6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EV6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EW6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EX6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EY6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EZ6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FA6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FB6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FC6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FD6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FE6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FF6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FG6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FH6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FI6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FJ6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FK6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FL6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FM6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FN6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FO6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FP6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FQ6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FR6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FS6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FT6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FU6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FV6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FW6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FX6" t="n">
+        <v>98</v>
+      </c>
+      <c r="FY6" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UP22SDN678901</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>6789</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DC7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DD7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DF7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DG7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DI7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DJ7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DK7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DL7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DN7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DO7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DP7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DQ7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DS7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DT7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DV7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DW7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DX7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DY7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DZ7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EA7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EB7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EC7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="ED7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EE7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EF7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EG7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EH7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EI7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EJ7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EK7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EL7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EM7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EN7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EO7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EP7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EQ7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="ER7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="ES7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="ET7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EU7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EV7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EW7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EX7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EY7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EZ7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FA7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FB7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FC7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FD7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FE7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FF7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FG7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FH7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FI7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FJ7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FK7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FL7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FM7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FN7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FO7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FP7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FQ7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FR7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FS7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FT7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FU7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FV7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FW7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FX7" t="n">
+        <v>60</v>
+      </c>
+      <c r="FY7" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UP23SWA345678</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4444</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CT8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CU8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DA8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DB8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DC8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DI8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DJ8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DK8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DL8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DN8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DO8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DP8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DQ8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DR8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DS8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DT8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DU8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DV8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DW8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DX8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DY8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DZ8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EA8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EB8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EC8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="ED8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EE8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EF8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EG8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EH8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EI8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EJ8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EK8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EL8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EM8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EN8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EO8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EP8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EQ8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="ER8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="ES8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="ET8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EU8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EV8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EW8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EX8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EY8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EZ8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FA8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FB8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FC8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FD8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="FE8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="FF8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="FG8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="FH8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="FI8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FJ8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FK8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FL8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FM8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FN8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FO8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FP8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FQ8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FR8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FS8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FT8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FU8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FV8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FW8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FX8" t="n">
+        <v>70</v>
+      </c>
+      <c r="FY8" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UP25SWN567890</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CT9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CU9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DA9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DB9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DC9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DI9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DJ9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DK9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DL9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DN9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DO9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DP9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DQ9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DS9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DT9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DU9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DV9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DW9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DX9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DY9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DZ9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EA9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EB9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EC9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="ED9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EE9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EF9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EG9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EH9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EI9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EJ9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EK9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EL9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EM9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EN9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EO9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EP9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EQ9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="ER9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="ES9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="ET9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EU9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EV9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EW9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EX9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EY9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EZ9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FA9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FB9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FC9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FD9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FE9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FF9" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FG9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FH9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FI9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FJ9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FK9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FL9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FM9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FN9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FO9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FP9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FQ9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FR9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FS9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FT9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FU9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FV9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FW9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FX9" t="n">
+        <v>52</v>
+      </c>
+      <c r="FY9" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>UP26SWN901234</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DC10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DD10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DE10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DF10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DG10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DI10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DJ10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DK10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DL10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DN10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DO10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="DP10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DQ10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DR10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DS10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="DT10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DU10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DV10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DW10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DX10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="DY10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="DZ10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EA10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EB10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EC10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="ED10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EE10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EF10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EG10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EH10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EI10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EJ10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EK10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EL10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EM10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EN10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EO10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="EP10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EQ10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="ER10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="ES10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="ET10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EU10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EV10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="EW10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="EX10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EY10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="EZ10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FA10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FB10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FC10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FD10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FE10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FF10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FG10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FH10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FI10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FJ10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FK10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FL10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FM10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FN10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FO10" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="FP10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FQ10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FR10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FS10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="FT10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FU10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="FV10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="FW10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="FX10" t="n">
+        <v>82</v>
+      </c>
+      <c r="FY10" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
